--- a/results/by_outcome/full_results_education_PGI_MI.xlsx
+++ b/results/by_outcome/full_results_education_PGI_MI.xlsx
@@ -486,10 +486,10 @@
         <v>#NUM!</v>
       </c>
       <c r="H2" t="n">
-        <v>0.588632892052824</v>
+        <v>0.589635135802955</v>
       </c>
       <c r="I2" t="n">
-        <v>0.28042484297219</v>
+        <v>0.277490201479415</v>
       </c>
       <c r="J2" t="e">
         <v>#NUM!</v>
@@ -507,7 +507,7 @@
         <v>#NUM!</v>
       </c>
       <c r="O2" t="n">
-        <v>0.411420401256562</v>
+        <v>0.410418258033766</v>
       </c>
     </row>
     <row r="3">
@@ -527,10 +527,10 @@
         <v>#NUM!</v>
       </c>
       <c r="F3" t="n">
-        <v>0.603695825461784</v>
+        <v>0.604491798755961</v>
       </c>
       <c r="G3" t="n">
-        <v>0.312032917347289</v>
+        <v>0.310759854013316</v>
       </c>
       <c r="H3" t="e">
         <v>#NUM!</v>
@@ -565,13 +565,13 @@
         <v>18</v>
       </c>
       <c r="C4" t="n">
-        <v>0.637314387588559</v>
+        <v>0.6372569072896</v>
       </c>
       <c r="D4" t="n">
-        <v>0.362776158086459</v>
+        <v>0.362833654974204</v>
       </c>
       <c r="E4" t="n">
-        <v>1.00009054567502</v>
+        <v>1.0000905622638</v>
       </c>
       <c r="F4" t="e">
         <v>#NUM!</v>
@@ -586,19 +586,19 @@
         <v>#NUM!</v>
       </c>
       <c r="J4" t="n">
-        <v>0.362743313229904</v>
+        <v>0.362800798845769</v>
       </c>
       <c r="K4" t="n">
-        <v>0.312004666656564</v>
+        <v>0.310731713388551</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0150615696308235</v>
+        <v>0.0148553176644629</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0486770880266578</v>
+        <v>0.0476174591879971</v>
       </c>
       <c r="N4" t="n">
-        <v>0.327066236287387</v>
+        <v>0.325587031053014</v>
       </c>
       <c r="O4" t="e">
         <v>#NUM!</v>
@@ -643,16 +643,16 @@
         <v>15</v>
       </c>
       <c r="C2" t="n">
-        <v>0.362743313229904</v>
+        <v>0.362800798845769</v>
       </c>
       <c r="D2" t="n">
-        <v>0.331497347395585</v>
+        <v>0.331968928328096</v>
       </c>
       <c r="E2" t="n">
-        <v>0.393989279064224</v>
+        <v>0.393632669363442</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000131735169066058</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000109440296186125</v>
       </c>
     </row>
     <row r="3">
@@ -663,16 +663,16 @@
         <v>15</v>
       </c>
       <c r="C3" t="n">
-        <v>0.327066236287387</v>
+        <v>0.325587031053014</v>
       </c>
       <c r="D3" t="n">
-        <v>0.296998994937347</v>
+        <v>0.29628298624296</v>
       </c>
       <c r="E3" t="n">
-        <v>0.357133477637428</v>
+        <v>0.354891075863069</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000802538121845811</v>
+        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000406328213746253</v>
       </c>
     </row>
     <row r="4">
@@ -683,16 +683,16 @@
         <v>15</v>
       </c>
       <c r="C4" t="n">
-        <v>0.411420401256562</v>
+        <v>0.410418258033766</v>
       </c>
       <c r="D4" t="n">
-        <v>0.380996347627972</v>
+        <v>0.380734668358299</v>
       </c>
       <c r="E4" t="n">
-        <v>0.441844454885152</v>
+        <v>0.440101847709234</v>
       </c>
       <c r="F4" t="n">
-        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000101324482959657</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000115750384732669</v>
       </c>
     </row>
     <row r="5">
@@ -703,16 +703,16 @@
         <v>15</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0843541649691749</v>
+        <v>0.084831226980752</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0697809421823482</v>
+        <v>0.0704789165175529</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0989273877560016</v>
+        <v>0.0991835374439512</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00000000000000000000000000000786771784063808</v>
+        <v>0.000000000000000000000000000000493239023983613</v>
       </c>
     </row>
   </sheetData>

--- a/results/by_outcome/full_results_education_PGI_MI.xlsx
+++ b/results/by_outcome/full_results_education_PGI_MI.xlsx
@@ -486,10 +486,10 @@
         <v>#NUM!</v>
       </c>
       <c r="H2" t="n">
-        <v>0.589635135802955</v>
+        <v>0.603163910827262</v>
       </c>
       <c r="I2" t="n">
-        <v>0.277490201479415</v>
+        <v>0.254136420194562</v>
       </c>
       <c r="J2" t="e">
         <v>#NUM!</v>
@@ -507,7 +507,7 @@
         <v>#NUM!</v>
       </c>
       <c r="O2" t="n">
-        <v>0.410418258033766</v>
+        <v>0.396884105134654</v>
       </c>
     </row>
     <row r="3">
@@ -527,10 +527,10 @@
         <v>#NUM!</v>
       </c>
       <c r="F3" t="n">
-        <v>0.604491798755961</v>
+        <v>0.618607104741289</v>
       </c>
       <c r="G3" t="n">
-        <v>0.310759854013316</v>
+        <v>0.29029448724729</v>
       </c>
       <c r="H3" t="e">
         <v>#NUM!</v>
@@ -565,13 +565,13 @@
         <v>18</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6372569072896</v>
+        <v>0.650307449823056</v>
       </c>
       <c r="D4" t="n">
-        <v>0.362833654974204</v>
+        <v>0.349772163355216</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0000905622638</v>
+        <v>1.00007961317827</v>
       </c>
       <c r="F4" t="e">
         <v>#NUM!</v>
@@ -586,19 +586,19 @@
         <v>#NUM!</v>
       </c>
       <c r="J4" t="n">
-        <v>0.362800798845769</v>
+        <v>0.349744319053397</v>
       </c>
       <c r="K4" t="n">
-        <v>0.310731713388551</v>
+        <v>0.290271377783965</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0148553176644629</v>
+        <v>0.0154419645464034</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0476174591879971</v>
+        <v>0.0471397860812565</v>
       </c>
       <c r="N4" t="n">
-        <v>0.325587031053014</v>
+        <v>0.305713342330368</v>
       </c>
       <c r="O4" t="e">
         <v>#NUM!</v>
@@ -643,16 +643,16 @@
         <v>15</v>
       </c>
       <c r="C2" t="n">
-        <v>0.362800798845769</v>
+        <v>0.349744319053397</v>
       </c>
       <c r="D2" t="n">
-        <v>0.331968928328096</v>
+        <v>0.320364749163839</v>
       </c>
       <c r="E2" t="n">
-        <v>0.393632669363442</v>
+        <v>0.379123888942955</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000109440296186125</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000021136758765949</v>
       </c>
     </row>
     <row r="3">
@@ -663,16 +663,16 @@
         <v>15</v>
       </c>
       <c r="C3" t="n">
-        <v>0.325587031053014</v>
+        <v>0.305713342330368</v>
       </c>
       <c r="D3" t="n">
-        <v>0.29628298624296</v>
+        <v>0.275272006487786</v>
       </c>
       <c r="E3" t="n">
-        <v>0.354891075863069</v>
+        <v>0.33615467817295</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000406328213746253</v>
+        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000425158819869177</v>
       </c>
     </row>
     <row r="4">
@@ -683,16 +683,16 @@
         <v>15</v>
       </c>
       <c r="C4" t="n">
-        <v>0.410418258033766</v>
+        <v>0.396884105134654</v>
       </c>
       <c r="D4" t="n">
-        <v>0.380734668358299</v>
+        <v>0.366307660511991</v>
       </c>
       <c r="E4" t="n">
-        <v>0.440101847709234</v>
+        <v>0.427460549757316</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000115750384732669</v>
+        <v>0.000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000000182834452897836</v>
       </c>
     </row>
     <row r="5">
@@ -703,16 +703,16 @@
         <v>15</v>
       </c>
       <c r="C5" t="n">
-        <v>0.084831226980752</v>
+        <v>0.0911707628042857</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0704789165175529</v>
+        <v>0.0753052243085104</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0991835374439512</v>
+        <v>0.107036301300061</v>
       </c>
       <c r="F5" t="n">
-        <v>0.000000000000000000000000000000493239023983613</v>
+        <v>0.0000000000000000000000000000200337751721148</v>
       </c>
     </row>
   </sheetData>
